--- a/events/Copenhagen_2015_WC/Copenhagen_2015_WC_Results.xlsx
+++ b/events/Copenhagen_2015_WC/Copenhagen_2015_WC_Results.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X742"/>
+  <dimension ref="A1:X753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8057,11 +8057,6 @@
           <t>00:00.560</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>45844</t>
-        </is>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>45846</t>
@@ -8312,11 +8307,6 @@
           <t>00:07.460</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>46597</t>
-        </is>
-      </c>
       <c r="T111" t="inlineStr">
         <is>
           <t>60648</t>
@@ -14717,11 +14707,6 @@
           <t>00:02.176</t>
         </is>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>46597</t>
-        </is>
-      </c>
       <c r="T200" t="inlineStr">
         <is>
           <t>60648</t>
@@ -26251,11 +26236,6 @@
           <t>00:00.084</t>
         </is>
       </c>
-      <c r="R358" t="inlineStr">
-        <is>
-          <t>45844</t>
-        </is>
-      </c>
       <c r="S358" t="inlineStr">
         <is>
           <t>45846</t>
@@ -33579,16 +33559,6 @@
           <t>00:02.044</t>
         </is>
       </c>
-      <c r="R459" t="inlineStr">
-        <is>
-          <t>46593</t>
-        </is>
-      </c>
-      <c r="S459" t="inlineStr">
-        <is>
-          <t>46596</t>
-        </is>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -39373,16 +39343,6 @@
           <t>00:00.988</t>
         </is>
       </c>
-      <c r="R540" t="inlineStr">
-        <is>
-          <t>46593</t>
-        </is>
-      </c>
-      <c r="S540" t="inlineStr">
-        <is>
-          <t>46596</t>
-        </is>
-      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -41170,16 +41130,6 @@
           <t>00:00.600</t>
         </is>
       </c>
-      <c r="R565" t="inlineStr">
-        <is>
-          <t>46593</t>
-        </is>
-      </c>
-      <c r="S565" t="inlineStr">
-        <is>
-          <t>46596</t>
-        </is>
-      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -48393,24 +48343,9 @@
           <t>00:01.360</t>
         </is>
       </c>
-      <c r="R663" t="inlineStr">
-        <is>
-          <t>46593</t>
-        </is>
-      </c>
       <c r="S663" t="inlineStr">
         <is>
           <t>60648</t>
-        </is>
-      </c>
-      <c r="T663" t="inlineStr">
-        <is>
-          <t>46596</t>
-        </is>
-      </c>
-      <c r="U663" t="inlineStr">
-        <is>
-          <t>46597</t>
         </is>
       </c>
     </row>
@@ -48731,11 +48666,6 @@
           <t>00:03.488</t>
         </is>
       </c>
-      <c r="R667" t="inlineStr">
-        <is>
-          <t>45844</t>
-        </is>
-      </c>
       <c r="S667" t="inlineStr">
         <is>
           <t>45846</t>
@@ -53248,70 +53178,62 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D730" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>heat</t>
-        </is>
-      </c>
-      <c r="F730" t="n">
-        <v>1</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G730" s="2" t="n">
-        <v>42154</v>
+        <v>42155</v>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L730" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M730" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N730" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="P730" t="inlineStr">
         <is>
-          <t>00:32.104</t>
+          <t>21:21.170</t>
+        </is>
+      </c>
+      <c r="Q730" t="inlineStr">
+        <is>
+          <t>01:32.650</t>
         </is>
       </c>
       <c r="R730" t="inlineStr">
         <is>
-          <t>42161</t>
-        </is>
-      </c>
-      <c r="S730" t="inlineStr">
-        <is>
-          <t>45847</t>
-        </is>
-      </c>
-      <c r="T730" t="inlineStr">
-        <is>
-          <t>42171</t>
-        </is>
-      </c>
-      <c r="U730" t="inlineStr">
-        <is>
-          <t>46764</t>
+          <t>45146</t>
         </is>
       </c>
     </row>
@@ -53328,70 +53250,62 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D731" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>heat</t>
-        </is>
-      </c>
-      <c r="F731" t="n">
-        <v>1</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G731" s="2" t="n">
-        <v>42154</v>
+        <v>42155</v>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L731" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="M731" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="N731" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P731" t="inlineStr">
         <is>
-          <t>00:32.444</t>
+          <t>21:47.740</t>
         </is>
       </c>
       <c r="Q731" t="inlineStr">
         <is>
-          <t>00:00.340</t>
+          <t>01:59.220</t>
         </is>
       </c>
       <c r="R731" t="inlineStr">
         <is>
-          <t>47621</t>
-        </is>
-      </c>
-      <c r="T731" t="inlineStr">
-        <is>
-          <t>52102</t>
-        </is>
-      </c>
-      <c r="U731" t="inlineStr">
-        <is>
-          <t>47627</t>
+          <t>48584</t>
         </is>
       </c>
     </row>
@@ -53408,75 +53322,62 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D732" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>heat</t>
-        </is>
-      </c>
-      <c r="F732" t="n">
-        <v>1</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G732" s="2" t="n">
-        <v>42154</v>
+        <v>42155</v>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L732" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="M732" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="N732" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="P732" t="inlineStr">
         <is>
-          <t>00:32.664</t>
+          <t>21:48.620</t>
         </is>
       </c>
       <c r="Q732" t="inlineStr">
         <is>
-          <t>00:00.560</t>
+          <t>02:00.100</t>
         </is>
       </c>
       <c r="R732" t="inlineStr">
         <is>
-          <t>42420</t>
-        </is>
-      </c>
-      <c r="S732" t="inlineStr">
-        <is>
-          <t>36446</t>
-        </is>
-      </c>
-      <c r="T732" t="inlineStr">
-        <is>
-          <t>42429</t>
-        </is>
-      </c>
-      <c r="U732" t="inlineStr">
-        <is>
-          <t>36584</t>
+          <t>42841</t>
         </is>
       </c>
     </row>
@@ -53493,75 +53394,62 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D733" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>heat</t>
-        </is>
-      </c>
-      <c r="F733" t="n">
-        <v>1</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G733" s="2" t="n">
-        <v>42154</v>
+        <v>42155</v>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L733" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M733" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="N733" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P733" t="inlineStr">
         <is>
-          <t>00:33.924</t>
+          <t>22:31.820</t>
         </is>
       </c>
       <c r="Q733" t="inlineStr">
         <is>
-          <t>00:01.820</t>
+          <t>02:43.300</t>
         </is>
       </c>
       <c r="R733" t="inlineStr">
         <is>
-          <t>42851</t>
-        </is>
-      </c>
-      <c r="S733" t="inlineStr">
-        <is>
-          <t>44010</t>
-        </is>
-      </c>
-      <c r="T733" t="inlineStr">
-        <is>
-          <t>42841</t>
-        </is>
-      </c>
-      <c r="U733" t="inlineStr">
-        <is>
-          <t>42351</t>
+          <t>45299</t>
         </is>
       </c>
     </row>
@@ -53578,75 +53466,51 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D734" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>heat</t>
-        </is>
-      </c>
-      <c r="F734" t="n">
-        <v>1</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G734" s="2" t="n">
-        <v>42154</v>
+        <v>42155</v>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>IRI</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L734" t="n">
-        <v>2</v>
-      </c>
-      <c r="M734" t="n">
-        <v>5</v>
-      </c>
-      <c r="N734" t="n">
-        <v>5</v>
-      </c>
-      <c r="P734" t="inlineStr">
-        <is>
-          <t>00:34.308</t>
-        </is>
-      </c>
-      <c r="Q734" t="inlineStr">
-        <is>
-          <t>00:02.204</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="R734" t="inlineStr">
         <is>
-          <t>36742</t>
-        </is>
-      </c>
-      <c r="S734" t="inlineStr">
-        <is>
-          <t>35993</t>
-        </is>
-      </c>
-      <c r="T734" t="inlineStr">
-        <is>
-          <t>52481</t>
-        </is>
-      </c>
-      <c r="U734" t="inlineStr">
-        <is>
-          <t>35981</t>
+          <t>47543</t>
+        </is>
+      </c>
+      <c r="X734" t="inlineStr">
+        <is>
+          <t>DSQ</t>
         </is>
       </c>
     </row>
@@ -53663,70 +53527,51 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D735" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>heat</t>
-        </is>
-      </c>
-      <c r="F735" t="n">
-        <v>2</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G735" s="2" t="n">
-        <v>42154</v>
+        <v>42155</v>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>16:50:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>URU</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L735" t="n">
-        <v>6</v>
-      </c>
-      <c r="M735" t="n">
-        <v>1</v>
-      </c>
-      <c r="N735" t="n">
-        <v>1</v>
-      </c>
-      <c r="P735" t="inlineStr">
-        <is>
-          <t>00:31.448</t>
-        </is>
+        <v>24</v>
       </c>
       <c r="R735" t="inlineStr">
         <is>
-          <t>42450</t>
-        </is>
-      </c>
-      <c r="S735" t="inlineStr">
-        <is>
-          <t>42455</t>
-        </is>
-      </c>
-      <c r="T735" t="inlineStr">
-        <is>
-          <t>42449</t>
-        </is>
-      </c>
-      <c r="U735" t="inlineStr">
-        <is>
-          <t>42464</t>
+          <t>61584</t>
+        </is>
+      </c>
+      <c r="X735" t="inlineStr">
+        <is>
+          <t>DSQ</t>
         </is>
       </c>
     </row>
@@ -53743,75 +53588,51 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D736" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>heat</t>
-        </is>
-      </c>
-      <c r="F736" t="n">
-        <v>2</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G736" s="2" t="n">
-        <v>42154</v>
+        <v>42155</v>
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>16:50:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>URU</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L736" t="n">
-        <v>7</v>
-      </c>
-      <c r="M736" t="n">
-        <v>2</v>
-      </c>
-      <c r="N736" t="n">
-        <v>2</v>
-      </c>
-      <c r="P736" t="inlineStr">
-        <is>
-          <t>00:32.396</t>
-        </is>
-      </c>
-      <c r="Q736" t="inlineStr">
-        <is>
-          <t>00:00.948</t>
-        </is>
+        <v>25</v>
       </c>
       <c r="R736" t="inlineStr">
         <is>
-          <t>46593</t>
-        </is>
-      </c>
-      <c r="S736" t="inlineStr">
-        <is>
-          <t>60648</t>
-        </is>
-      </c>
-      <c r="T736" t="inlineStr">
-        <is>
-          <t>46596</t>
-        </is>
-      </c>
-      <c r="U736" t="inlineStr">
-        <is>
-          <t>46597</t>
+          <t>61586</t>
+        </is>
+      </c>
+      <c r="X736" t="inlineStr">
+        <is>
+          <t>DNF</t>
         </is>
       </c>
     </row>
@@ -53828,65 +53649,51 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D737" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>heat</t>
-        </is>
-      </c>
-      <c r="F737" t="n">
-        <v>2</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G737" s="2" t="n">
-        <v>42154</v>
+        <v>42155</v>
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>16:50:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L737" t="n">
-        <v>4</v>
-      </c>
-      <c r="M737" t="n">
-        <v>3</v>
-      </c>
-      <c r="N737" t="n">
-        <v>3</v>
-      </c>
-      <c r="P737" t="inlineStr">
-        <is>
-          <t>00:32.536</t>
-        </is>
-      </c>
-      <c r="Q737" t="inlineStr">
-        <is>
-          <t>00:01.088</t>
-        </is>
-      </c>
-      <c r="T737" t="inlineStr">
-        <is>
-          <t>36151</t>
-        </is>
-      </c>
-      <c r="U737" t="inlineStr">
-        <is>
-          <t>42139</t>
+        <v>1</v>
+      </c>
+      <c r="R737" t="inlineStr">
+        <is>
+          <t>41774</t>
+        </is>
+      </c>
+      <c r="X737" t="inlineStr">
+        <is>
+          <t>DNS</t>
         </is>
       </c>
     </row>
@@ -53903,26 +53710,28 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D738" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>heat</t>
-        </is>
-      </c>
-      <c r="F738" t="n">
-        <v>2</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G738" s="2" t="n">
-        <v>42154</v>
+        <v>42155</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>16:50:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -53932,46 +53741,20 @@
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L738" t="n">
         <v>3</v>
       </c>
-      <c r="M738" t="n">
-        <v>4</v>
-      </c>
-      <c r="N738" t="n">
-        <v>4</v>
-      </c>
-      <c r="P738" t="inlineStr">
-        <is>
-          <t>00:32.696</t>
-        </is>
-      </c>
-      <c r="Q738" t="inlineStr">
-        <is>
-          <t>00:01.248</t>
-        </is>
-      </c>
       <c r="R738" t="inlineStr">
         <is>
-          <t>52210</t>
-        </is>
-      </c>
-      <c r="S738" t="inlineStr">
-        <is>
-          <t>36578</t>
-        </is>
-      </c>
-      <c r="T738" t="inlineStr">
-        <is>
-          <t>42428</t>
-        </is>
-      </c>
-      <c r="U738" t="inlineStr">
-        <is>
-          <t>61538</t>
+          <t>42420</t>
+        </is>
+      </c>
+      <c r="X738" t="inlineStr">
+        <is>
+          <t>DNS</t>
         </is>
       </c>
     </row>
@@ -53988,82 +53771,58 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D739" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>heat</t>
-        </is>
-      </c>
-      <c r="F739" t="n">
-        <v>2</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="G739" s="2" t="n">
-        <v>42154</v>
+        <v>42155</v>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>16:50:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L739" t="n">
-        <v>5</v>
-      </c>
-      <c r="M739" t="n">
-        <v>5</v>
-      </c>
-      <c r="N739" t="n">
-        <v>5</v>
-      </c>
-      <c r="P739" t="inlineStr">
-        <is>
-          <t>00:33.484</t>
-        </is>
-      </c>
-      <c r="Q739" t="inlineStr">
-        <is>
-          <t>00:02.036</t>
-        </is>
+        <v>8</v>
       </c>
       <c r="R739" t="inlineStr">
         <is>
-          <t>45844</t>
-        </is>
-      </c>
-      <c r="S739" t="inlineStr">
-        <is>
-          <t>45846</t>
-        </is>
-      </c>
-      <c r="T739" t="inlineStr">
-        <is>
-          <t>61242</t>
-        </is>
-      </c>
-      <c r="U739" t="inlineStr">
-        <is>
-          <t>47415</t>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="X739" t="inlineStr">
+        <is>
+          <t>DNS</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -54073,11 +53832,11 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D740" t="n">
-        <v>200</v>
+        <v>5000</v>
       </c>
       <c r="E740" t="inlineStr">
         <is>
@@ -54094,43 +53853,37 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>13:09:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>95</t>
         </is>
       </c>
       <c r="L740" t="n">
-        <v>4</v>
-      </c>
-      <c r="M740" t="n">
-        <v>1</v>
-      </c>
-      <c r="N740" t="n">
-        <v>1</v>
-      </c>
-      <c r="P740" t="inlineStr">
-        <is>
-          <t>00:51.224</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="R740" t="inlineStr">
         <is>
-          <t>61143</t>
+          <t>36604</t>
+        </is>
+      </c>
+      <c r="X740" t="inlineStr">
+        <is>
+          <t>DNS</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -54140,7 +53893,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D741" t="n">
@@ -54148,61 +53901,69 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="F741" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="F741" t="n">
+        <v>1</v>
       </c>
       <c r="G741" s="2" t="n">
-        <v>42155</v>
+        <v>42154</v>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>13:09:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>901</t>
         </is>
       </c>
       <c r="L741" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M741" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N741" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P741" t="inlineStr">
         <is>
-          <t>00:53.844</t>
-        </is>
-      </c>
-      <c r="Q741" t="inlineStr">
-        <is>
-          <t>00:02.620</t>
+          <t>00:32.104</t>
         </is>
       </c>
       <c r="R741" t="inlineStr">
         <is>
-          <t>61144</t>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="S741" t="inlineStr">
+        <is>
+          <t>45847</t>
+        </is>
+      </c>
+      <c r="T741" t="inlineStr">
+        <is>
+          <t>42171</t>
+        </is>
+      </c>
+      <c r="U741" t="inlineStr">
+        <is>
+          <t>46764</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -54212,7 +53973,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="D742" t="n">
@@ -54220,52 +53981,916 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="F742" t="n">
+        <v>1</v>
+      </c>
+      <c r="G742" s="2" t="n">
+        <v>42154</v>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="L742" t="n">
+        <v>4</v>
+      </c>
+      <c r="M742" t="n">
+        <v>2</v>
+      </c>
+      <c r="N742" t="n">
+        <v>2</v>
+      </c>
+      <c r="P742" t="inlineStr">
+        <is>
+          <t>00:32.444</t>
+        </is>
+      </c>
+      <c r="Q742" t="inlineStr">
+        <is>
+          <t>00:00.340</t>
+        </is>
+      </c>
+      <c r="R742" t="inlineStr">
+        <is>
+          <t>47621</t>
+        </is>
+      </c>
+      <c r="T742" t="inlineStr">
+        <is>
+          <t>52102</t>
+        </is>
+      </c>
+      <c r="U742" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>200</v>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="F743" t="n">
+        <v>1</v>
+      </c>
+      <c r="G743" s="2" t="n">
+        <v>42154</v>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="L743" t="n">
+        <v>3</v>
+      </c>
+      <c r="M743" t="n">
+        <v>3</v>
+      </c>
+      <c r="N743" t="n">
+        <v>3</v>
+      </c>
+      <c r="P743" t="inlineStr">
+        <is>
+          <t>00:32.664</t>
+        </is>
+      </c>
+      <c r="Q743" t="inlineStr">
+        <is>
+          <t>00:00.560</t>
+        </is>
+      </c>
+      <c r="R743" t="inlineStr">
+        <is>
+          <t>42420</t>
+        </is>
+      </c>
+      <c r="S743" t="inlineStr">
+        <is>
+          <t>36446</t>
+        </is>
+      </c>
+      <c r="T743" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
+      <c r="U743" t="inlineStr">
+        <is>
+          <t>36584</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="D744" t="n">
+        <v>200</v>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="F744" t="n">
+        <v>1</v>
+      </c>
+      <c r="G744" s="2" t="n">
+        <v>42154</v>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="L744" t="n">
+        <v>5</v>
+      </c>
+      <c r="M744" t="n">
+        <v>4</v>
+      </c>
+      <c r="N744" t="n">
+        <v>4</v>
+      </c>
+      <c r="P744" t="inlineStr">
+        <is>
+          <t>00:33.924</t>
+        </is>
+      </c>
+      <c r="Q744" t="inlineStr">
+        <is>
+          <t>00:01.820</t>
+        </is>
+      </c>
+      <c r="R744" t="inlineStr">
+        <is>
+          <t>42851</t>
+        </is>
+      </c>
+      <c r="S744" t="inlineStr">
+        <is>
+          <t>44010</t>
+        </is>
+      </c>
+      <c r="T744" t="inlineStr">
+        <is>
+          <t>42841</t>
+        </is>
+      </c>
+      <c r="U744" t="inlineStr">
+        <is>
+          <t>42351</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="D745" t="n">
+        <v>200</v>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="F745" t="n">
+        <v>1</v>
+      </c>
+      <c r="G745" s="2" t="n">
+        <v>42154</v>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>16:45:00</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="L745" t="n">
+        <v>2</v>
+      </c>
+      <c r="M745" t="n">
+        <v>5</v>
+      </c>
+      <c r="N745" t="n">
+        <v>5</v>
+      </c>
+      <c r="P745" t="inlineStr">
+        <is>
+          <t>00:34.308</t>
+        </is>
+      </c>
+      <c r="Q745" t="inlineStr">
+        <is>
+          <t>00:02.204</t>
+        </is>
+      </c>
+      <c r="R745" t="inlineStr">
+        <is>
+          <t>36742</t>
+        </is>
+      </c>
+      <c r="S745" t="inlineStr">
+        <is>
+          <t>35993</t>
+        </is>
+      </c>
+      <c r="T745" t="inlineStr">
+        <is>
+          <t>52481</t>
+        </is>
+      </c>
+      <c r="U745" t="inlineStr">
+        <is>
+          <t>35981</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>200</v>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="F746" t="n">
+        <v>2</v>
+      </c>
+      <c r="G746" s="2" t="n">
+        <v>42154</v>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>16:50:00</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="L746" t="n">
+        <v>6</v>
+      </c>
+      <c r="M746" t="n">
+        <v>1</v>
+      </c>
+      <c r="N746" t="n">
+        <v>1</v>
+      </c>
+      <c r="P746" t="inlineStr">
+        <is>
+          <t>00:31.448</t>
+        </is>
+      </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>42450</t>
+        </is>
+      </c>
+      <c r="S746" t="inlineStr">
+        <is>
+          <t>42455</t>
+        </is>
+      </c>
+      <c r="T746" t="inlineStr">
+        <is>
+          <t>42449</t>
+        </is>
+      </c>
+      <c r="U746" t="inlineStr">
+        <is>
+          <t>42464</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>200</v>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="F747" t="n">
+        <v>2</v>
+      </c>
+      <c r="G747" s="2" t="n">
+        <v>42154</v>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>16:50:00</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="L747" t="n">
+        <v>7</v>
+      </c>
+      <c r="M747" t="n">
+        <v>2</v>
+      </c>
+      <c r="N747" t="n">
+        <v>2</v>
+      </c>
+      <c r="P747" t="inlineStr">
+        <is>
+          <t>00:32.396</t>
+        </is>
+      </c>
+      <c r="Q747" t="inlineStr">
+        <is>
+          <t>00:00.948</t>
+        </is>
+      </c>
+      <c r="S747" t="inlineStr">
+        <is>
+          <t>60648</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>200</v>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="F748" t="n">
+        <v>2</v>
+      </c>
+      <c r="G748" s="2" t="n">
+        <v>42154</v>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>16:50:00</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="L748" t="n">
+        <v>4</v>
+      </c>
+      <c r="M748" t="n">
+        <v>3</v>
+      </c>
+      <c r="N748" t="n">
+        <v>3</v>
+      </c>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>00:32.536</t>
+        </is>
+      </c>
+      <c r="Q748" t="inlineStr">
+        <is>
+          <t>00:01.088</t>
+        </is>
+      </c>
+      <c r="T748" t="inlineStr">
+        <is>
+          <t>36151</t>
+        </is>
+      </c>
+      <c r="U748" t="inlineStr">
+        <is>
+          <t>42139</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>200</v>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="F749" t="n">
+        <v>2</v>
+      </c>
+      <c r="G749" s="2" t="n">
+        <v>42154</v>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>16:50:00</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="L749" t="n">
+        <v>3</v>
+      </c>
+      <c r="M749" t="n">
+        <v>4</v>
+      </c>
+      <c r="N749" t="n">
+        <v>4</v>
+      </c>
+      <c r="P749" t="inlineStr">
+        <is>
+          <t>00:32.696</t>
+        </is>
+      </c>
+      <c r="Q749" t="inlineStr">
+        <is>
+          <t>00:01.248</t>
+        </is>
+      </c>
+      <c r="R749" t="inlineStr">
+        <is>
+          <t>52210</t>
+        </is>
+      </c>
+      <c r="S749" t="inlineStr">
+        <is>
+          <t>36578</t>
+        </is>
+      </c>
+      <c r="T749" t="inlineStr">
+        <is>
+          <t>42428</t>
+        </is>
+      </c>
+      <c r="U749" t="inlineStr">
+        <is>
+          <t>61538</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>K4</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>200</v>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="F750" t="n">
+        <v>2</v>
+      </c>
+      <c r="G750" s="2" t="n">
+        <v>42154</v>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>16:50:00</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="L750" t="n">
+        <v>5</v>
+      </c>
+      <c r="M750" t="n">
+        <v>5</v>
+      </c>
+      <c r="N750" t="n">
+        <v>5</v>
+      </c>
+      <c r="P750" t="inlineStr">
+        <is>
+          <t>00:33.484</t>
+        </is>
+      </c>
+      <c r="Q750" t="inlineStr">
+        <is>
+          <t>00:02.036</t>
+        </is>
+      </c>
+      <c r="S750" t="inlineStr">
+        <is>
+          <t>45846</t>
+        </is>
+      </c>
+      <c r="T750" t="inlineStr">
+        <is>
+          <t>61242</t>
+        </is>
+      </c>
+      <c r="U750" t="inlineStr">
+        <is>
+          <t>47415</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>200</v>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
           <t>final</t>
         </is>
       </c>
-      <c r="F742" t="inlineStr">
+      <c r="F751" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G742" s="2" t="n">
+      <c r="G751" s="2" t="n">
         <v>42155</v>
       </c>
-      <c r="H742" t="inlineStr">
+      <c r="H751" t="inlineStr">
         <is>
           <t>13:09:00</t>
         </is>
       </c>
-      <c r="I742" t="inlineStr">
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>UZB</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="L751" t="n">
+        <v>4</v>
+      </c>
+      <c r="M751" t="n">
+        <v>1</v>
+      </c>
+      <c r="N751" t="n">
+        <v>1</v>
+      </c>
+      <c r="P751" t="inlineStr">
+        <is>
+          <t>00:51.224</t>
+        </is>
+      </c>
+      <c r="R751" t="inlineStr">
+        <is>
+          <t>61143</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>200</v>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="n">
+        <v>42155</v>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>13:09:00</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>UZB</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="L752" t="n">
+        <v>6</v>
+      </c>
+      <c r="M752" t="n">
+        <v>2</v>
+      </c>
+      <c r="N752" t="n">
+        <v>2</v>
+      </c>
+      <c r="P752" t="inlineStr">
+        <is>
+          <t>00:53.844</t>
+        </is>
+      </c>
+      <c r="Q752" t="inlineStr">
+        <is>
+          <t>00:02.620</t>
+        </is>
+      </c>
+      <c r="R752" t="inlineStr">
+        <is>
+          <t>61144</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>SENIOR</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>200</v>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G753" s="2" t="n">
+        <v>42155</v>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>13:09:00</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
         <is>
           <t>DEN</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr">
+      <c r="K753" t="inlineStr">
         <is>
           <t>903</t>
         </is>
       </c>
-      <c r="L742" t="n">
+      <c r="L753" t="n">
         <v>5</v>
       </c>
-      <c r="M742" t="n">
+      <c r="M753" t="n">
         <v>3</v>
       </c>
-      <c r="N742" t="n">
+      <c r="N753" t="n">
         <v>3</v>
       </c>
-      <c r="P742" t="inlineStr">
+      <c r="P753" t="inlineStr">
         <is>
           <t>01:08.252</t>
         </is>
       </c>
-      <c r="Q742" t="inlineStr">
+      <c r="Q753" t="inlineStr">
         <is>
           <t>00:17.028</t>
         </is>
       </c>
-      <c r="R742" t="inlineStr">
+      <c r="R753" t="inlineStr">
         <is>
           <t>61594</t>
         </is>
@@ -54282,7 +54907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D277"/>
+  <dimension ref="A1:D273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56026,17 +56651,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>46596</t>
+          <t>41774</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mustafa</t>
+          <t>Jeremy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GULBAHAR</t>
+          <t>HAKALA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -56048,39 +56673,39 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>41774</t>
+          <t>52762</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jeremy</t>
+          <t>Arezou</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HAKALA</t>
+          <t>HAKIMIMOGHADDAM</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>52762</t>
+          <t>61478</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arezou</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HAKIMIMOGHADDAM</t>
+          <t>HANIFEHZADEH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -56092,17 +56717,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HANIFEHZADEH</t>
+          <t>HANNAH</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -56114,17 +56739,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Henriette</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HANNAH</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -56136,17 +56761,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Henriette</t>
+          <t>Verena</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>HANTL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -56158,39 +56783,39 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>36670</t>
+          <t>42514</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Verena</t>
+          <t>Gordan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HANTL</t>
+          <t>HARBRECHT</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>42514</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Gordan</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HARBRECHT</t>
+          <t>HEATH</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -56202,61 +56827,61 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HEATH</t>
+          <t>HERING</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>42519</t>
+          <t>35993</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Lars</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HERING</t>
+          <t>HJEMDAL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lars</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HJEMDAL</t>
+          <t>HOFF</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -56268,166 +56893,166 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>54144</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HOFF</t>
+          <t>HOFMANN</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HOFMANN</t>
+          <t>HORNSBY</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Jieyi</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HORNSBY</t>
+          <t>HUANG</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jieyi</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HUANG</t>
+          <t>INCOLLINGO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>36565</t>
+          <t>51914</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Maja</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>INCOLLINGO</t>
+          <t>IRGENS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>51914</t>
+          <t>52231</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Maja</t>
+          <t>Ernest</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IRGENS</t>
+          <t>IRNAZAROV</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>52231</t>
+          <t>42550</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ernest</t>
+          <t>Abir</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IRNAZAROV</t>
+          <t>ISMAIL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>42550</t>
+          <t>42549</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Abir</t>
+          <t>Afef</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -56444,17 +57069,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>42549</t>
+          <t>44824</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Afef</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
+          <t>JANICKA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -56466,39 +57091,39 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>44824</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Jeppe</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JANICKA</t>
+          <t>JENSBY</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>42351</t>
+          <t>42488</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jeppe</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>JENSBY</t>
+          <t>JESSOP</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -56510,17 +57135,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>42488</t>
+          <t>42441</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JESSOP</t>
+          <t>JEZIERSKI</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -56532,83 +57157,83 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>42441</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Karin</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JEZIERSKI</t>
+          <t>JOHANSSON</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>51625</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Karin</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JOHANSSON</t>
+          <t>KACZMAREK</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>51625</t>
+          <t>60010</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Jiamei</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KACZMAREK</t>
+          <t>KANG</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>60010</t>
+          <t>45142</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jiamei</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KANG</t>
+          <t>KATRINECZ</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -56620,56 +57245,56 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>45142</t>
+          <t>47674</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>Ildar</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KATRINECZ</t>
+          <t>KAYUMOV</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>47674</t>
+          <t>53568</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ildar</t>
+          <t>Hediye</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>KAYUMOV</t>
+          <t>KAZEMI</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>53568</t>
+          <t>61472</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hediye</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -56686,171 +57311,171 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Mirziyodjon</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KAZEMI</t>
+          <t>KHOJIEV</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>36473</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mirziyodjon</t>
+          <t>Youjin</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>KHOJIEV</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Youjin</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>KIRAJ</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>42559</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Inna</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KIRAJ</t>
+          <t>KLINOVA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>42559</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Inna</t>
+          <t>Gerasim</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>KLINOVA</t>
+          <t>KOCHNEV</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>56339</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Gerasim</t>
+          <t>Kseniya</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KOCHNEV</t>
+          <t>KOCHNEVA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>56339</t>
+          <t>42512</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Kseniya</t>
+          <t>Felix</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>KOCHNEVA</t>
+          <t>KOENIG</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>42512</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Felix</t>
+          <t>Mátyás</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KOENIG</t>
+          <t>KOLESZÁR</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -56862,17 +57487,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>45146</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mátyás</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>KOLESZÁR</t>
+          <t>KRETSCHMER</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -56884,61 +57509,61 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>49522</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Spikkeland</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KRETSCHMER</t>
+          <t>KRISTIANE</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>49522</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Spikkeland</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>KRISTIANE</t>
+          <t>KUJAWSKI</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Fabian</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KUJAWSKI</t>
+          <t>KUX</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -56950,17 +57575,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>46597</t>
+          <t>54675</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ozturk</t>
+          <t>Felix</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KURU</t>
+          <t>LANDES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -56972,39 +57597,39 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>36669</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fabian</t>
+          <t>Mira</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>KUX</t>
+          <t>LARSEN</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>54675</t>
+          <t>60648</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Felix</t>
+          <t>Borislav</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LANDES</t>
+          <t>LAZIC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -57016,61 +57641,61 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>42257</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mira</t>
+          <t>Andres</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LARSEN</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>60648</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Borislav</t>
+          <t>Hyeran</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LAZIC</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>52253</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Guiqiang</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -57082,17 +57707,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>60009</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Hyeran</t>
+          <t>Yue</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -57104,12 +57729,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>52253</t>
+          <t>52169</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Guiqiang</t>
+          <t>Zhangli</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -57119,19 +57744,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>60009</t>
+          <t>52256</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Yue</t>
+          <t>Zhenyu</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -57141,24 +57766,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>52169</t>
+          <t>65863</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Zhangli</t>
+          <t>Lasma</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LIEPA</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -57170,17 +57795,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>52256</t>
+          <t>52103</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Zhenyu</t>
+          <t>Johan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LILJA</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -57192,61 +57817,61 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>65863</t>
+          <t>52099</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Lasma</t>
+          <t>Joakim</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LIEPA</t>
+          <t>LINDBERG</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>52103</t>
+          <t>42663</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Johan</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>LILJA</t>
+          <t>LISIECKA</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>52099</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Joakim</t>
+          <t>Bo</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LINDBERG</t>
+          <t>LIU</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -57258,17 +57883,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>42663</t>
+          <t>52167</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Martyna</t>
+          <t>Haiping</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LISIECKA</t>
+          <t>LIU</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -57280,39 +57905,39 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>60014</t>
+          <t>58730</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bo</t>
+          <t>Noémi</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LIU</t>
+          <t>LUCZ</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>52167</t>
+          <t>52173</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Haiping</t>
+          <t>Qing</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LIU</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -57324,17 +57949,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>58730</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Noémi</t>
+          <t>Mie</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LUCZ</t>
+          <t>MADSEN</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -57346,17 +57971,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>52173</t>
+          <t>61458</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Qing</t>
+          <t>Mahsa</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MAGHANJOUGHI</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -57368,17 +57993,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>61594</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mie</t>
+          <t>Eszter</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MADSEN</t>
+          <t>MALCSINER</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -57390,61 +58015,61 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>61458</t>
+          <t>61253</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Mahsa</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MAGHANJOUGHI</t>
+          <t>MALFESI</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>45131</t>
+          <t>42139</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Eszter</t>
+          <t>Ruslan</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MALCSINER</t>
+          <t>MAMUTOV</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>61253</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MALFESI</t>
+          <t>MARON</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -57456,17 +58081,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>42139</t>
+          <t>52161</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ruslan</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MAMUTOV</t>
+          <t>MARQUES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -57478,39 +58103,39 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Hayleigh-Jayne</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MARON</t>
+          <t>MASON</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>52161</t>
+          <t>60759</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Mykola</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MARQUES</t>
+          <t>MATVIICHUK</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -57522,39 +58147,39 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>42487</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Hayleigh-Jayne</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MASON</t>
+          <t>MCCOOMBS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>60759</t>
+          <t>51826</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Mykola</t>
+          <t>Marty</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MATVIICHUK</t>
+          <t>MCDOWELL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -57566,17 +58191,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MCCOOMBS</t>
+          <t>MCKEEVER</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -57588,17 +58213,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>51826</t>
+          <t>42463</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Marty</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MCDOWELL</t>
+          <t>MEHAK</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -57610,17 +58235,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Vadim</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MCKEEVER</t>
+          <t>MENKOV</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -57632,17 +58257,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>47621</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Petter</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MEHAK</t>
+          <t>MENNING</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -57654,17 +58279,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>51786</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Vadim</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MENKOV</t>
+          <t>MEUNIER</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -57676,17 +58301,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>47621</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Petter</t>
+          <t>Serik</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MENNING</t>
+          <t>MIRBEKOV</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -57698,17 +58323,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>51786</t>
+          <t>35721</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MEUNIER</t>
+          <t>MITTELSTEDT</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -57720,17 +58345,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Serik</t>
+          <t>Aleksey</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MIRBEKOV</t>
+          <t>MOCHALOV</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -57742,17 +58367,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>61067</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Yassine</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MITTELSTEDT</t>
+          <t>MOHAMED</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -57764,17 +58389,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>52228</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Aleksey</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MOCHALOV</t>
+          <t>MORNEAU</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -57786,17 +58411,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>61067</t>
+          <t>42283</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Yassine</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MOHAMED</t>
+          <t>MRABET</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -57808,17 +58433,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>53052</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MORNEAU</t>
+          <t>MUELLER</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -57830,17 +58455,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>42283</t>
+          <t>47634</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MRABET</t>
+          <t>NATHELL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -57852,17 +58477,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>53052</t>
+          <t>53082</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MUELLER</t>
+          <t>NOE</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -57874,39 +58499,39 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>44826</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>NATHELL</t>
+          <t>NOGA</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>53082</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Yul</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>NOE</t>
+          <t>OELTZE</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -57918,39 +58543,39 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>44826</t>
+          <t>61556</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Elling</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>NOGA</t>
+          <t>OFTEDAL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>42510</t>
+          <t>52761</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Yul</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>OELTZE</t>
+          <t>OJAGHI</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -57962,17 +58587,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>61556</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Elling</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>OFTEDAL</t>
+          <t>OLDERSHAW</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -57984,17 +58609,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>52761</t>
+          <t>66520</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Kristjan</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>OJAGHI</t>
+          <t>ORAS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -58006,83 +58631,83 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Genevieve</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>OLDERSHAW</t>
+          <t>ORTON</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>66520</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Kristjan</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ORAS</t>
+          <t>PALDANIUS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>42467</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Genevieve</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ORTON</t>
+          <t>PANNECOUCKE</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>61358</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Cintia</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PALDANIUS</t>
+          <t>PAPP</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -58094,17 +58719,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Artuur</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PANNECOUCKE</t>
+          <t>PETERS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -58116,17 +58741,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>61358</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Cintia</t>
+          <t>Hermien</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PAPP</t>
+          <t>PETERS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -58138,83 +58763,83 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>42842</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Artuur</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>PETERS</t>
+          <t>PETERSEN</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>41793</t>
+          <t>54934</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Hermien</t>
+          <t>Albert</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PETERS</t>
+          <t>PETERSSON</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>42842</t>
+          <t>45847</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PETERSEN</t>
+          <t>PHILLIPS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>54934</t>
+          <t>49620</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>Orion</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PETERSSON</t>
+          <t>PILO</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -58226,17 +58851,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>61255</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Pierre-Luc</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>PHILLIPS</t>
+          <t>POULIN</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -58248,17 +58873,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Orion</t>
+          <t>René</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PILO</t>
+          <t>POULSEN</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -58270,17 +58895,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>61255</t>
+          <t>42841</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Pierre-Luc</t>
+          <t>Casper</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>POULIN</t>
+          <t>PRETZMANN</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -58292,83 +58917,83 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>René</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>POULSEN</t>
+          <t>PULAWSKA</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>42841</t>
+          <t>54080</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Casper</t>
+          <t>Malgorzata</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>PRETZMANN</t>
+          <t>PULAWSKA</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>44828</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>PULAWSKA</t>
+          <t>PUTTO</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>54080</t>
+          <t>61143</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Malgorzata</t>
+          <t>Dilnoza</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>PULAWSKA</t>
+          <t>RAKHMATOVA</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -58380,17 +59005,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>PUTTO</t>
+          <t>REARDON</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -58402,39 +59027,39 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>61143</t>
+          <t>36230</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Dilnoza</t>
+          <t>Kristian</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>RAKHMATOVA</t>
+          <t>REEVES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>61459</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>Reza</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>REARDON</t>
+          <t>REISI</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -58446,39 +59071,39 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>52168</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Kristian</t>
+          <t>Wenjun</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>REEVES</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>61459</t>
+          <t>36666</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Reza</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>REISI</t>
+          <t>RENDSCHMIDT</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -58490,39 +59115,39 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>61561</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Wenjun</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>REPELE</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>42906</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>RENDSCHMIDT</t>
+          <t>REUSCHENBACH</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -58534,39 +59159,39 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>60678</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>REPELE</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>42906</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>REUSCHENBACH</t>
+          <t>RICCHETTI</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -58578,61 +59203,61 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>60678</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>RICHARD</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>61165</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Mariecarmen</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>RICCHETTI</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Maxime</t>
+          <t>Sebastián</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>RICHARD</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -58644,39 +59269,39 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>61165</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Mariecarmen</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>ROSOLSKI</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>61583</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Sebastián</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -58688,39 +59313,39 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ROSOLSKI</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>36234</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>RUTHERFORD</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -58732,17 +59357,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>42483</t>
+          <t>52739</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>RUTISHAUSER</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -58754,83 +59379,83 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>36234</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Yuliana</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>RUTHERFORD</t>
+          <t>SALAKHOVA</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>RUTISHAUSER</t>
+          <t>SALBU</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>36170</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Yuliana</t>
+          <t>Daniele</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SALAKHOVA</t>
+          <t>SANTINI</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>42513</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SALBU</t>
+          <t>SCHMUDE</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -58842,17 +59467,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Daniele</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>SANTINI</t>
+          <t>SCHOFIELD</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -58864,39 +59489,39 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>SCHMUDE</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>61392</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>SCHOFIELD</t>
+          <t>SCOTT</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -58908,17 +59533,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>52211</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Sára</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>SEPRENYI</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -58930,61 +59555,61 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>61392</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Genevieve</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SCOTT</t>
+          <t>SEVIGNY</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>52211</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Sára</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>SEPRENYI</t>
+          <t>SIEMIONOWSKI</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>42963</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Genevieve</t>
+          <t>Rebeka</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SEVIGNY</t>
+          <t>SIMON</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -58996,83 +59621,83 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>60184</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Fanni</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SIEMIONOWSKI</t>
+          <t>SIMÁN</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>42963</t>
+          <t>61557</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Rebeka</t>
+          <t>Jon</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>SIMON</t>
+          <t>SMEBYE</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>60184</t>
+          <t>36667</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Fanni</t>
+          <t>Kai</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SIMÁN</t>
+          <t>SPENNER</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>61557</t>
+          <t>42596</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Jon</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>SMEBYE</t>
+          <t>STABNO</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -59084,61 +59709,61 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>STENSILS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>36667</t>
+          <t>42146</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Kai</t>
+          <t>Kira</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>SPENNER</t>
+          <t>STEPANOVA</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>42596</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Kostja</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>STABNO</t>
+          <t>STROINSKI</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -59150,61 +59775,61 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>47622</t>
+          <t>56071</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kaspar</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>STENSILS</t>
+          <t>SULA</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>42146</t>
+          <t>52260</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Kira</t>
+          <t>Xinchang</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>STEPANOVA</t>
+          <t>SUN</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>47627</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Kostja</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>STROINSKI</t>
+          <t>SVANQVIST</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -59216,39 +59841,39 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>56071</t>
+          <t>45143</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Kaspar</t>
+          <t>Ágnes</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>SULA</t>
+          <t>SZABÓ</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>52260</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Xinchang</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>SUN</t>
+          <t>SZANDRACH</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -59260,61 +59885,61 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>47627</t>
+          <t>60064</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Anett</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SVANQVIST</t>
+          <t>SZILÁGYI</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>45143</t>
+          <t>42446</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Ágnes</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>SZABÓ</t>
+          <t>SÉVIGNY</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Carlo</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>SZANDRACH</t>
+          <t>TACCHINI</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -59326,17 +59951,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>60064</t>
+          <t>61457</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Anett</t>
+          <t>Maedeh</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>SZILÁGYI</t>
+          <t>TAHMASEBIBAROUGH</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -59348,39 +59973,39 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>42446</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Tamara</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SÉVIGNY</t>
+          <t>TAKÁCS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>47543</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Carlo</t>
+          <t>Ahmadreza</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>TACCHINI</t>
+          <t>TALEBIAN</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -59392,83 +60017,83 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>61457</t>
+          <t>42171</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Maedeh</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>TAHMASEBIBAROUGH</t>
+          <t>TAME</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>42494</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Tamara</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>TAKÁCS</t>
+          <t>TARDIOLI</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>47543</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Ahmadreza</t>
+          <t>Amalie</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>TALEBIAN</t>
+          <t>THOMSEN</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>42171</t>
+          <t>66559</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Tarmo</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>TAME</t>
+          <t>TOOTSI</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -59480,17 +60105,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>42494</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>TARDIOLI</t>
+          <t>TORNEO</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -59502,39 +60127,39 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>42349</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Amalie</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>THOMSEN</t>
+          <t>TROPIN</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>66559</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tarmo</t>
+          <t>Lars</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>TOOTSI</t>
+          <t>ULLVANG</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -59546,39 +60171,39 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>42420</t>
+          <t>52235</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Olga</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>TORNEO</t>
+          <t>UMARALIEVA</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>TROPIN</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -59590,17 +60215,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>36742</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Lars</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>ULLVANG</t>
+          <t>VASILYEV</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -59612,17 +60237,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Olga</t>
+          <t>Oona</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>UMARALIEVA</t>
+          <t>VASKO</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -59634,105 +60259,105 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>42484</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Hannah</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>VAUGHAN</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>52489</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Christina</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>VASILYEV</t>
+          <t>VEDOE</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>35729</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Oona</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>VASKO</t>
+          <t>VERCH</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>42484</t>
+          <t>36595</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Niklas</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>VAUGHAN</t>
+          <t>VETTANEN</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Christina</t>
+          <t>Ida</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>VEDOE</t>
+          <t>VILLUMSEN</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -59744,83 +60369,83 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Sabine</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>VERCH</t>
+          <t>VOLZ</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>36595</t>
+          <t>36222</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Niklas</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>VETTANEN</t>
+          <t>WALKER</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>42346</t>
+          <t>42161</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Ida</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>VILLUMSEN</t>
+          <t>WALLACE</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>60075</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Sabine</t>
+          <t>Feng</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>VOLZ</t>
+          <t>WANG</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -59832,39 +60457,39 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>36222</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Longkui</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>WALKER</t>
+          <t>WANG</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>41742</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Kenny</t>
+          <t>Riwei</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>WALLACE</t>
+          <t>WANG</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -59876,17 +60501,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>60075</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Feng</t>
+          <t>Conny</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>WANG</t>
+          <t>WASSMUTH</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -59898,17 +60523,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Longkui</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>WANG</t>
+          <t>WATKINS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -59920,17 +60545,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Riwei</t>
+          <t>Joeri</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>WANG</t>
+          <t>WECKX</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -59942,61 +60567,61 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>52481</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Conny</t>
+          <t>Per</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>WASSMUTH</t>
+          <t>WESSEL</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>47624</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Moa</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>WATKINS</t>
+          <t>WIKBERG</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>47415</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Joeri</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>WECKX</t>
+          <t>WOOD</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -60008,17 +60633,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>52481</t>
+          <t>52257</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Per</t>
+          <t>Xiaojun</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>WESSEL</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -60030,17 +60655,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>47624</t>
+          <t>52171</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Moa</t>
+          <t>Yanan</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>WIKBERG</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -60052,17 +60677,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>47415</t>
+          <t>61026</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Haitao</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>WOOD</t>
+          <t>XU</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -60074,17 +60699,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>52257</t>
+          <t>62121</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Xiaojun</t>
+          <t>Jung</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>YUSUNG</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -60096,39 +60721,39 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>52171</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Yanan</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>ZAKRAJSEK</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>60006</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Haitao</t>
+          <t>Dong</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>XU</t>
+          <t>ZHANG</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -60140,17 +60765,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>46593</t>
+          <t>41741</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Cagribey</t>
+          <t>Pengfei</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>YILDIRIM</t>
+          <t>ZHENG</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -60162,17 +60787,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>62121</t>
+          <t>61024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Jung</t>
+          <t>Haisai</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>YUSUNG</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -60184,17 +60809,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Jost</t>
+          <t>Peng</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>ZAKRAJSEK</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -60206,39 +60831,39 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>60006</t>
+          <t>52182</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Dong</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>ZHANG</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>41741</t>
+          <t>61025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Pengfei</t>
+          <t>Yubo</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>ZHENG</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -60250,17 +60875,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>61024</t>
+          <t>52249</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Haisai</t>
+          <t>Shuibin</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>ZHOU</t>
+          <t>ZHUANG</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -60272,108 +60897,20 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>60015</t>
+          <t>61144</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Peng</t>
+          <t>Nulufar</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>ZHOU</t>
+          <t>ZOKIROVA</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>52182</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Yu</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>ZHOU</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>61025</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Yubo</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>ZHOU</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>52249</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Shuibin</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>ZHUANG</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>61144</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Nulufar</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>ZOKIROVA</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
         <is>
           <t>F</t>
         </is>

--- a/events/Copenhagen_2015_WC/Copenhagen_2015_WC_Results.xlsx
+++ b/events/Copenhagen_2015_WC/Copenhagen_2015_WC_Results.xlsx
@@ -8057,6 +8057,11 @@
           <t>00:00.560</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>45844</t>
+        </is>
+      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>45846</t>
@@ -8307,6 +8312,11 @@
           <t>00:07.460</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>46597</t>
+        </is>
+      </c>
       <c r="T111" t="inlineStr">
         <is>
           <t>60648</t>
@@ -14707,6 +14717,11 @@
           <t>00:02.176</t>
         </is>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>46597</t>
+        </is>
+      </c>
       <c r="T200" t="inlineStr">
         <is>
           <t>60648</t>
@@ -26236,6 +26251,11 @@
           <t>00:00.084</t>
         </is>
       </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>45844</t>
+        </is>
+      </c>
       <c r="S358" t="inlineStr">
         <is>
           <t>45846</t>
@@ -33559,6 +33579,16 @@
           <t>00:02.044</t>
         </is>
       </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>46593</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>46596</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -39343,6 +39373,16 @@
           <t>00:00.988</t>
         </is>
       </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>46593</t>
+        </is>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>46596</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -41130,6 +41170,16 @@
           <t>00:00.600</t>
         </is>
       </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>46593</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>46596</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -48343,9 +48393,24 @@
           <t>00:01.360</t>
         </is>
       </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>46593</t>
+        </is>
+      </c>
       <c r="S663" t="inlineStr">
         <is>
           <t>60648</t>
+        </is>
+      </c>
+      <c r="T663" t="inlineStr">
+        <is>
+          <t>46596</t>
+        </is>
+      </c>
+      <c r="U663" t="inlineStr">
+        <is>
+          <t>46597</t>
         </is>
       </c>
     </row>
@@ -48666,6 +48731,11 @@
           <t>00:03.488</t>
         </is>
       </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>45844</t>
+        </is>
+      </c>
       <c r="S667" t="inlineStr">
         <is>
           <t>45846</t>
@@ -54439,9 +54509,24 @@
           <t>00:00.948</t>
         </is>
       </c>
+      <c r="R747" t="inlineStr">
+        <is>
+          <t>46593</t>
+        </is>
+      </c>
       <c r="S747" t="inlineStr">
         <is>
           <t>60648</t>
+        </is>
+      </c>
+      <c r="T747" t="inlineStr">
+        <is>
+          <t>46596</t>
+        </is>
+      </c>
+      <c r="U747" t="inlineStr">
+        <is>
+          <t>46597</t>
         </is>
       </c>
     </row>
@@ -54667,6 +54752,11 @@
       <c r="Q750" t="inlineStr">
         <is>
           <t>00:02.036</t>
+        </is>
+      </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>45844</t>
         </is>
       </c>
       <c r="S750" t="inlineStr">
@@ -54907,7 +54997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D273"/>
+  <dimension ref="A1:D277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60916,6 +61006,94 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>45844</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>46597</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Ozturk</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>KURU</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>46593</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Cagribey</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>YILDIRIM</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>46596</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Mustafa</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>GULBAHAR</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Copenhagen_2015_WC/Copenhagen_2015_WC_Results.xlsx
+++ b/events/Copenhagen_2015_WC/Copenhagen_2015_WC_Results.xlsx
@@ -3192,6 +3192,11 @@
           <t>60655</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>60653</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3317,6 +3322,16 @@
           <t>01:46.852</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5432,6 +5447,11 @@
           <t>00:04.520</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6672,6 +6692,11 @@
           <t>52750</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6817,6 +6842,11 @@
           <t>53082</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7032,6 +7062,11 @@
           <t>36595</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7977,6 +8012,11 @@
           <t>03:07.740</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>42511</t>
+        </is>
+      </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>42906</t>
@@ -8642,6 +8682,11 @@
           <t>00:01.376</t>
         </is>
       </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
       <c r="T115" t="inlineStr">
         <is>
           <t>36151</t>
@@ -11442,6 +11487,11 @@
           <t>60655</t>
         </is>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>60653</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12502,6 +12552,11 @@
           <t>00:06.888</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13482,6 +13537,11 @@
           <t>52750</t>
         </is>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13627,6 +13687,11 @@
           <t>53082</t>
         </is>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -15212,9 +15277,19 @@
           <t>00:00.280</t>
         </is>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="T206" t="inlineStr">
         <is>
           <t>42146</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>42148</t>
         </is>
       </c>
     </row>
@@ -15452,6 +15527,11 @@
           <t>52211</t>
         </is>
       </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>60653</t>
+        </is>
+      </c>
       <c r="T209" t="inlineStr">
         <is>
           <t>60655</t>
@@ -15537,6 +15617,11 @@
           <t>36472</t>
         </is>
       </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
       <c r="U210" t="inlineStr">
         <is>
           <t>36473</t>
@@ -17772,6 +17857,11 @@
           <t>00:05.780</t>
         </is>
       </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -18142,6 +18232,11 @@
           <t>52211</t>
         </is>
       </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>60653</t>
+        </is>
+      </c>
       <c r="T246" t="inlineStr">
         <is>
           <t>60655</t>
@@ -18482,6 +18577,11 @@
           <t>36472</t>
         </is>
       </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
       <c r="U250" t="inlineStr">
         <is>
           <t>36473</t>
@@ -19037,6 +19137,11 @@
           <t>00:03.052</t>
         </is>
       </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -21521,6 +21626,11 @@
           <t>00:07.560</t>
         </is>
       </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -22668,6 +22778,16 @@
           <t>00:02.340</t>
         </is>
       </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -23825,6 +23945,11 @@
           <t>00:05.244</t>
         </is>
       </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -24642,6 +24767,11 @@
           <t>52750</t>
         </is>
       </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -25243,6 +25373,11 @@
           <t>60759</t>
         </is>
       </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>66277</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -26169,6 +26304,11 @@
           <t>03:09.660</t>
         </is>
       </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>42511</t>
+        </is>
+      </c>
       <c r="S357" t="inlineStr">
         <is>
           <t>42906</t>
@@ -26425,6 +26565,11 @@
           <t>00:04.608</t>
         </is>
       </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
       <c r="T360" t="inlineStr">
         <is>
           <t>36151</t>
@@ -27105,6 +27250,16 @@
           <t>42146</t>
         </is>
       </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -27420,6 +27575,11 @@
           <t>36472</t>
         </is>
       </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
       <c r="U372" t="inlineStr">
         <is>
           <t>36473</t>
@@ -28250,6 +28410,11 @@
           <t>61472</t>
         </is>
       </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>61474</t>
+        </is>
+      </c>
       <c r="U382" t="inlineStr">
         <is>
           <t>52764</t>
@@ -30245,6 +30410,11 @@
           <t>00:00.716</t>
         </is>
       </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -30585,6 +30755,11 @@
           <t>00:03.816</t>
         </is>
       </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>42548</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -32704,6 +32879,11 @@
           <t>00:02.876</t>
         </is>
       </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>60653</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -34634,6 +34814,11 @@
           <t>00:03.124</t>
         </is>
       </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
       <c r="S473" t="inlineStr">
         <is>
           <t>61291</t>
@@ -36564,6 +36749,11 @@
           <t>00:04.108</t>
         </is>
       </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>42548</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -38208,6 +38398,11 @@
           <t>00:02.932</t>
         </is>
       </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>60653</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -40738,6 +40933,11 @@
           <t>00:00.704</t>
         </is>
       </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>60653</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -42208,6 +42408,11 @@
           <t>00:05.136</t>
         </is>
       </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -43066,6 +43271,16 @@
           <t>42146</t>
         </is>
       </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -43717,6 +43932,11 @@
           <t>01:53.504</t>
         </is>
       </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -43784,6 +44004,11 @@
           <t>00:00.232</t>
         </is>
       </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -44283,6 +44508,11 @@
           <t>00:20.480</t>
         </is>
       </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>42548</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -45538,6 +45768,11 @@
       <c r="L625" t="n">
         <v>3</v>
       </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
       <c r="X625" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -48567,6 +48802,11 @@
           <t>00:02.168</t>
         </is>
       </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
       <c r="T665" t="inlineStr">
         <is>
           <t>36151</t>
@@ -48813,9 +49053,19 @@
           <t>00:36.528</t>
         </is>
       </c>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="T668" t="inlineStr">
         <is>
           <t>42146</t>
+        </is>
+      </c>
+      <c r="U668" t="inlineStr">
+        <is>
+          <t>42148</t>
         </is>
       </c>
     </row>
@@ -49484,6 +49734,11 @@
           <t>52211</t>
         </is>
       </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>60653</t>
+        </is>
+      </c>
       <c r="T676" t="inlineStr">
         <is>
           <t>60655</t>
@@ -49869,6 +50124,11 @@
           <t>60759</t>
         </is>
       </c>
+      <c r="S681" t="inlineStr">
+        <is>
+          <t>66277</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -50727,6 +50987,11 @@
       <c r="L693" t="n">
         <v>2</v>
       </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>66277</t>
+        </is>
+      </c>
       <c r="X693" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -54592,6 +54857,11 @@
       <c r="Q748" t="inlineStr">
         <is>
           <t>00:01.088</t>
+        </is>
+      </c>
+      <c r="R748" t="inlineStr">
+        <is>
+          <t>42144</t>
         </is>
       </c>
       <c r="T748" t="inlineStr">
@@ -54997,7 +55267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D277"/>
+  <dimension ref="A1:D293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61094,6 +61364,358 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Ilia</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SHTOKALOV</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>ANIUSHINA</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Miika</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>NYKAENEN</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Mikhail</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>PAVLOV</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Aleksandr</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SERGEEV</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Svetlana</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>CHERNIGOVSKAYA</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>42356</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Nils Jensen</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>BOE</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>42511</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>SCHUBERT</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>42548</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>HOUCINE</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Mads Brandt</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>PEDERSEN</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Sun Ja</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>LEE</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>60653</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Marjorie Elizabeth</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>BATES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>61474</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Kiana</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>KAMALZADEH</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>66277</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Adnan</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>ALIEV</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Saeid</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>FAZLOULA</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Copenhagen_2015_WC/Copenhagen_2015_WC_Results.xlsx
+++ b/events/Copenhagen_2015_WC/Copenhagen_2015_WC_Results.xlsx
@@ -2897,6 +2897,11 @@
           <t>00:00.408</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr">
         <is>
           <t>42337</t>
@@ -11702,6 +11707,11 @@
           <t>00:01.208</t>
         </is>
       </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>42337</t>
@@ -15197,6 +15207,11 @@
           <t>00:00.144</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>42337</t>
@@ -22629,6 +22644,11 @@
           <t>00:01.840</t>
         </is>
       </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S307" t="inlineStr">
         <is>
           <t>42337</t>
@@ -27325,6 +27345,11 @@
           <t>00:01.512</t>
         </is>
       </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S369" t="inlineStr">
         <is>
           <t>42337</t>
@@ -28830,6 +28855,11 @@
           <t>00:02.120</t>
         </is>
       </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>61302</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -29380,6 +29410,11 @@
           <t>00:01.560</t>
         </is>
       </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>55865</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -34494,6 +34529,11 @@
           <t>01:48.080</t>
         </is>
       </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S469" t="inlineStr">
         <is>
           <t>42337</t>
@@ -35584,6 +35624,11 @@
           <t>00:01.756</t>
         </is>
       </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>55865</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -35789,6 +35834,11 @@
           <t>00:04.424</t>
         </is>
       </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>61302</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -40012,6 +40062,11 @@
           <t>00:00.096</t>
         </is>
       </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>55865</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -43435,6 +43490,11 @@
           <t>00:01.604</t>
         </is>
       </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S593" t="inlineStr">
         <is>
           <t>42337</t>
@@ -49304,6 +49364,11 @@
           <t>00:00.224</t>
         </is>
       </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S671" t="inlineStr">
         <is>
           <t>42337</t>
@@ -51396,6 +51461,11 @@
       <c r="Q699" t="inlineStr">
         <is>
           <t>00:30.270</t>
+        </is>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>42844</t>
         </is>
       </c>
     </row>
@@ -55267,7 +55337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D293"/>
+  <dimension ref="A1:D296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61716,6 +61786,72 @@
         </is>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>JØRGENSEN</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>61302</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Claus</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>KREGBERG</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>55865</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Sergei</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>TOKARNITSKYI</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
